--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yuanhao.Li\OneDrive - Mowi ASA\work_files\CrossFit\2025 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7D0E24-7840-494E-BD89-57CF03830C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E26745E-D33C-4AD8-AB76-E23C181A71F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
   <sheets>
     <sheet name="ScoreF" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
   <si>
     <t>Team</t>
   </si>
@@ -180,6 +180,15 @@
     <t>Listefyllet</t>
   </si>
   <si>
+    <t>BPCs Fittest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mats og Emil </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snorre og Yngve </t>
+  </si>
+  <si>
     <t xml:space="preserve">Joakim og Alexander </t>
   </si>
   <si>
@@ -294,6 +303,9 @@
     <t>Frode og Fredrik</t>
   </si>
   <si>
+    <t>Runar og Amund</t>
+  </si>
+  <si>
     <t>Rakan og Kristian</t>
   </si>
   <si>
@@ -313,15 +325,6 @@
   </si>
   <si>
     <t>Second4</t>
-  </si>
-  <si>
-    <t>Høns med Gøns</t>
-  </si>
-  <si>
-    <t>Ulven og Kaninen</t>
-  </si>
-  <si>
-    <t>Chippendales</t>
   </si>
 </sst>
 </file>
@@ -718,13 +721,13 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K1" t="s">
         <v>6</v>
@@ -736,125 +739,727 @@
         <v>8</v>
       </c>
       <c r="N1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="O1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>122</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>59</v>
+      </c>
+      <c r="I2">
+        <v>29</v>
+      </c>
+      <c r="J2">
+        <f>H2+I2</f>
+        <v>88</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>50</v>
+      </c>
+      <c r="N2">
+        <v>8</v>
+      </c>
+      <c r="O2">
+        <v>12</v>
+      </c>
+      <c r="P2">
+        <v>1580</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>83</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>47</v>
+      </c>
+      <c r="I3">
+        <v>41</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J23" si="0">H3+I3</f>
+        <v>88</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>60</v>
+      </c>
+      <c r="N3">
+        <v>9</v>
+      </c>
+      <c r="O3">
+        <v>40</v>
+      </c>
+      <c r="P3">
+        <v>1580</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>77</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>64</v>
+      </c>
+      <c r="I4">
+        <v>69</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>133</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>35</v>
+      </c>
+      <c r="N4">
+        <v>9</v>
+      </c>
+      <c r="O4">
+        <v>30</v>
+      </c>
+      <c r="P4">
+        <v>1580</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>96</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>67</v>
+      </c>
+      <c r="I5">
+        <v>40</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>107</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>70</v>
+      </c>
+      <c r="N5">
+        <v>9</v>
+      </c>
+      <c r="O5">
+        <v>20</v>
+      </c>
+      <c r="P5">
+        <v>1580</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>98</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>63</v>
+      </c>
+      <c r="I6">
+        <v>39</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>62</v>
+      </c>
+      <c r="N6">
+        <v>10</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1542</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>124</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>62</v>
+      </c>
+      <c r="I7">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>107</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>53</v>
+      </c>
+      <c r="N7">
+        <v>7</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7">
+        <v>1580</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>83</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>70</v>
+      </c>
+      <c r="I8">
+        <v>48</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>41</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1558</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>79</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>31</v>
+      </c>
+      <c r="I9">
+        <v>73</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>104</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>53</v>
+      </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1565</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>79</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>74</v>
+      </c>
+      <c r="I10">
+        <v>41</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>115</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>56</v>
+      </c>
+      <c r="N10">
+        <v>10</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1571</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
       </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>101</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>73</v>
+      </c>
+      <c r="I11">
+        <v>38</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>111</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>55</v>
+      </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1535</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>120</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>49</v>
+      </c>
+      <c r="I12">
+        <v>29</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>63</v>
+      </c>
+      <c r="N12">
+        <v>7</v>
+      </c>
+      <c r="O12">
+        <v>31</v>
+      </c>
+      <c r="P12">
+        <v>1580</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>107</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>74</v>
+      </c>
+      <c r="I13">
+        <v>46</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>35</v>
+      </c>
+      <c r="N13">
+        <v>8</v>
+      </c>
+      <c r="O13">
+        <v>51</v>
+      </c>
+      <c r="P13">
+        <v>1580</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>95</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>27</v>
+      </c>
+      <c r="I14">
+        <v>34</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>53</v>
+      </c>
+      <c r="N14">
+        <v>9</v>
+      </c>
+      <c r="O14">
+        <v>44</v>
+      </c>
+      <c r="P14">
+        <v>1580</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>85</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>48</v>
+      </c>
+      <c r="I15">
+        <v>42</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>56</v>
+      </c>
+      <c r="N15">
+        <v>7</v>
+      </c>
+      <c r="O15">
+        <v>50</v>
+      </c>
+      <c r="P15">
+        <v>1580</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -864,61 +1469,405 @@
       <c r="B16" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>95</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>55</v>
+      </c>
+      <c r="I16">
+        <v>47</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>66</v>
+      </c>
+      <c r="N16">
+        <v>8</v>
+      </c>
+      <c r="O16">
+        <v>19</v>
+      </c>
+      <c r="P16">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>86</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>52</v>
+      </c>
+      <c r="I17">
+        <v>49</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>63</v>
+      </c>
+      <c r="N17">
+        <v>10</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>102</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>46</v>
+      </c>
+      <c r="I18">
+        <v>48</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>68</v>
+      </c>
+      <c r="N18">
+        <v>8</v>
+      </c>
+      <c r="O18">
+        <v>14</v>
+      </c>
+      <c r="P18">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>96</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>49</v>
+      </c>
+      <c r="I19">
+        <v>60</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>109</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>64</v>
+      </c>
+      <c r="N19">
+        <v>10</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>115</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>59</v>
+      </c>
+      <c r="I20">
+        <v>34</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="K20">
+        <v>10</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>55</v>
+      </c>
+      <c r="N20">
+        <v>10</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>79</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>46</v>
+      </c>
+      <c r="I21">
+        <v>64</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>65</v>
+      </c>
+      <c r="N21">
+        <v>9</v>
+      </c>
+      <c r="O21">
+        <v>29</v>
+      </c>
+      <c r="P21">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>85</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>59</v>
+      </c>
+      <c r="I22">
+        <v>61</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="K22">
+        <v>10</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>47</v>
+      </c>
+      <c r="N22">
+        <v>10</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>95</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>69</v>
+      </c>
+      <c r="I23">
+        <v>48</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>117</v>
+      </c>
+      <c r="K23">
+        <v>10</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>72</v>
+      </c>
+      <c r="N23">
+        <v>7</v>
+      </c>
+      <c r="O23">
+        <v>24</v>
+      </c>
+      <c r="P23">
+        <v>1580</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AFD43C6-B370-4D80-A6DE-9002700F80AB}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -963,13 +1912,13 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K1" t="s">
         <v>6</v>
@@ -981,149 +1930,931 @@
         <v>8</v>
       </c>
       <c r="N1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="O1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
       </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>81</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>39</v>
+      </c>
+      <c r="I2">
+        <v>26</v>
+      </c>
+      <c r="J2">
+        <f>H2+I2</f>
+        <v>65</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>50</v>
+      </c>
+      <c r="N2">
+        <v>8</v>
+      </c>
+      <c r="O2">
+        <v>32</v>
+      </c>
+      <c r="P2">
+        <v>1880</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
       </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>77</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>57</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J19" si="0">H3+I3</f>
+        <v>102</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>60</v>
+      </c>
+      <c r="N3">
+        <v>9</v>
+      </c>
+      <c r="O3">
+        <v>29</v>
+      </c>
+      <c r="P3">
+        <v>1880</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
       </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>112</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>28</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>35</v>
+      </c>
+      <c r="N4">
+        <v>9</v>
+      </c>
+      <c r="O4">
+        <v>9</v>
+      </c>
+      <c r="P4">
+        <v>1880</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
       </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>118</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>27</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>70</v>
+      </c>
+      <c r="N5">
+        <v>9</v>
+      </c>
+      <c r="O5">
+        <v>37</v>
+      </c>
+      <c r="P5">
+        <v>1880</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>48</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>122</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>38</v>
+      </c>
+      <c r="I6">
+        <v>41</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>62</v>
+      </c>
+      <c r="N6">
+        <v>10</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1861</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
         <v>38</v>
       </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>116</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>38</v>
+      </c>
+      <c r="I7">
+        <v>46</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>53</v>
+      </c>
+      <c r="N7">
+        <v>10</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1842</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
       </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>80</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>60</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>41</v>
+      </c>
+      <c r="N8">
+        <v>8</v>
+      </c>
+      <c r="O8">
+        <v>46</v>
+      </c>
+      <c r="P8">
+        <v>1880</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
       </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>108</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>43</v>
+      </c>
+      <c r="I9">
+        <v>33</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>53</v>
+      </c>
+      <c r="N9">
+        <v>7</v>
+      </c>
+      <c r="O9">
+        <v>33</v>
+      </c>
+      <c r="P9">
+        <v>1880</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
         <v>41</v>
       </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>95</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>30</v>
+      </c>
+      <c r="I10">
+        <v>70</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>56</v>
+      </c>
+      <c r="N10">
+        <v>10</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1849</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
       </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>92</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>61</v>
+      </c>
+      <c r="I11">
+        <v>47</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>55</v>
+      </c>
+      <c r="N11">
+        <v>9</v>
+      </c>
+      <c r="O11">
+        <v>31</v>
+      </c>
+      <c r="P11">
+        <v>1880</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>43</v>
       </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>105</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>37</v>
+      </c>
+      <c r="I12">
+        <v>65</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>63</v>
+      </c>
+      <c r="N12">
+        <v>8</v>
+      </c>
+      <c r="O12">
+        <v>4</v>
+      </c>
+      <c r="P12">
+        <v>1880</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
         <v>44</v>
       </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>92</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>70</v>
+      </c>
+      <c r="I13">
+        <v>34</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>104</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>35</v>
+      </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1838</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>49</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>108</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>60</v>
+      </c>
+      <c r="I14">
+        <v>66</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>53</v>
+      </c>
+      <c r="N14">
+        <v>9</v>
+      </c>
+      <c r="O14">
+        <v>37</v>
+      </c>
+      <c r="P14">
+        <v>1880</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
         <v>45</v>
       </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>108</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>72</v>
+      </c>
+      <c r="I15">
+        <v>34</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>56</v>
+      </c>
+      <c r="N15">
+        <v>10</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1850</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>98</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>52</v>
+      </c>
+      <c r="I16">
+        <v>44</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>66</v>
+      </c>
+      <c r="N16">
+        <v>9</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>113</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>58</v>
+      </c>
+      <c r="I17">
+        <v>68</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>63</v>
+      </c>
+      <c r="N17">
+        <v>8</v>
+      </c>
+      <c r="O17">
+        <v>23</v>
+      </c>
+      <c r="P17">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>87</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>51</v>
+      </c>
+      <c r="I18">
+        <v>53</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>104</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>68</v>
+      </c>
+      <c r="N18">
+        <v>7</v>
+      </c>
+      <c r="O18">
+        <v>54</v>
+      </c>
+      <c r="P18">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>76</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>30</v>
+      </c>
+      <c r="I19">
+        <v>56</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>64</v>
+      </c>
+      <c r="N19">
+        <v>9</v>
+      </c>
+      <c r="O19">
+        <v>54</v>
+      </c>
+      <c r="P19">
+        <v>1880</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yuanhao.Li\OneDrive - Mowi ASA\work_files\CrossFit\2025 halloween games\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\crossfit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7D0E24-7840-494E-BD89-57CF03830C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BBB905-73D4-4E97-A24B-1DDD96873DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
   <sheets>
     <sheet name="ScoreF" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="97">
   <si>
     <t>Team</t>
   </si>
@@ -81,18 +81,12 @@
     <t>Forced in the Rain</t>
   </si>
   <si>
-    <t>Team Dødsløft</t>
-  </si>
-  <si>
     <t>Apple Bottom Cleans</t>
   </si>
   <si>
     <t>Mom and The Bomb</t>
   </si>
   <si>
-    <t>The Bet(h)s eller Kålhodene</t>
-  </si>
-  <si>
     <t>Blodpumpene</t>
   </si>
   <si>
@@ -150,9 +144,6 @@
     <t>Attack of the Clones</t>
   </si>
   <si>
-    <t>Biceps &amp; Brass Knuckles</t>
-  </si>
-  <si>
     <t>Telebuddies</t>
   </si>
   <si>
@@ -180,15 +171,6 @@
     <t>Listefyllet</t>
   </si>
   <si>
-    <t xml:space="preserve">Joakim og Alexander </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rakan og Kristian </t>
-  </si>
-  <si>
-    <t>Ida og Gjertrud</t>
-  </si>
-  <si>
     <t>Marie og Karen Anna</t>
   </si>
   <si>
@@ -322,6 +304,30 @@
   </si>
   <si>
     <t>Chippendales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hate it our Louvre it </t>
+  </si>
+  <si>
+    <t>Kålhodene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead Lift </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuns with Nuts </t>
+  </si>
+  <si>
+    <t>Bleikfeit</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Knoll og Tott</t>
+  </si>
+  <si>
+    <t>Heine og Eivind</t>
   </si>
 </sst>
 </file>
@@ -679,23 +685,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78915278-2E53-45F4-B4B1-D169831C96F1}">
-  <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.85546875" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.42578125" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.7109375" customWidth="1"/>
-    <col min="13" max="13" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="7.85546875" customWidth="1"/>
+    <col min="1" max="2" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.88671875" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.44140625" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.6640625" customWidth="1"/>
+    <col min="13" max="13" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -718,13 +724,13 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="K1" t="s">
         <v>6</v>
@@ -736,194 +742,375 @@
         <v>8</v>
       </c>
       <c r="N1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>53</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>54</v>
       </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>55</v>
       </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>56</v>
       </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>58</v>
       </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>59</v>
       </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>60</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>61</v>
       </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>62</v>
       </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" t="s">
-        <v>31</v>
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B21">
-    <sortCondition ref="B2:B21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B20">
+    <sortCondition ref="B2:B20"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -933,14 +1120,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AFD43C6-B370-4D80-A6DE-9002700F80AB}">
-  <dimension ref="A1:P18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -963,13 +1150,13 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="K1" t="s">
         <v>6</v>
@@ -981,149 +1168,319 @@
         <v>8</v>
       </c>
       <c r="N1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
         <v>91</v>
       </c>
-      <c r="P1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>69</v>
       </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>70</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>73</v>
       </c>
-      <c r="B6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>75</v>
       </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>76</v>
       </c>
-      <c r="B9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>77</v>
       </c>
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>78</v>
       </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B18" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" t="s">
-        <v>48</v>
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -1133,10 +1490,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE0349A-1D2A-4BA4-9394-3B33A3DE0436}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1144,7 +1501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1152,7 +1509,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1160,7 +1517,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1168,7 +1525,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1176,7 +1533,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1184,7 +1541,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1192,7 +1549,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1200,7 +1557,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1208,7 +1565,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1216,7 +1573,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1224,7 +1581,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1232,7 +1589,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1240,7 +1597,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1248,7 +1605,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1256,7 +1613,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1264,7 +1621,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1272,7 +1629,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1280,7 +1637,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1288,7 +1645,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1296,7 +1653,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1304,7 +1661,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1312,7 +1669,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1320,7 +1677,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1328,7 +1685,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1336,7 +1693,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1344,7 +1701,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1352,7 +1709,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1360,7 +1717,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1368,7 +1725,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1376,12 +1733,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
         <v>27</v>
+      </c>
+      <c r="G31" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\crossfit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BBB905-73D4-4E97-A24B-1DDD96873DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317B70AF-5C04-4901-B7A7-D9F6FFA2291C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
   <sheets>
     <sheet name="ScoreF" sheetId="1" r:id="rId1"/>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\crossfit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317B70AF-5C04-4901-B7A7-D9F6FFA2291C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540689EB-0AFD-4B62-A03F-00D13729BB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -767,6 +767,31 @@
       <c r="E2">
         <v>183</v>
       </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>45</v>
+      </c>
+      <c r="I2">
+        <v>47.5</v>
+      </c>
+      <c r="J2">
+        <f>H2+I2</f>
+        <v>92.5</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>95</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -784,6 +809,31 @@
       <c r="E3">
         <v>291</v>
       </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>57.5</v>
+      </c>
+      <c r="I3">
+        <v>65</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J22" si="0">H3+I3</f>
+        <v>122.5</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>154</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -801,6 +851,31 @@
       <c r="E4">
         <v>237</v>
       </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>57.5</v>
+      </c>
+      <c r="I4">
+        <v>45</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>102.5</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>98</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -818,6 +893,31 @@
       <c r="E5">
         <v>278</v>
       </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>55</v>
+      </c>
+      <c r="I5">
+        <v>75</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>130</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>99</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -835,6 +935,31 @@
       <c r="E6">
         <v>280</v>
       </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>55</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>138</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -852,6 +977,31 @@
       <c r="E7">
         <v>264</v>
       </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>35</v>
+      </c>
+      <c r="I7">
+        <v>57.5</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>92.5</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>90</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -869,6 +1019,31 @@
       <c r="E8">
         <v>276</v>
       </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>70</v>
+      </c>
+      <c r="I8">
+        <v>55</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>132</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -886,6 +1061,31 @@
       <c r="E9">
         <v>179</v>
       </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>37.5</v>
+      </c>
+      <c r="I9">
+        <v>52.5</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>55</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -903,6 +1103,31 @@
       <c r="E10">
         <v>234</v>
       </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>45</v>
+      </c>
+      <c r="I10">
+        <v>57.5</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>102.5</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>95</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -920,6 +1145,31 @@
       <c r="E11">
         <v>280</v>
       </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>42.5</v>
+      </c>
+      <c r="I11">
+        <v>57.5</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>117</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -937,6 +1187,31 @@
       <c r="E12">
         <v>273</v>
       </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>52.5</v>
+      </c>
+      <c r="I12">
+        <v>52.5</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>97</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -954,6 +1229,31 @@
       <c r="E13">
         <v>233</v>
       </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>40</v>
+      </c>
+      <c r="I13">
+        <v>52.5</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>92.5</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>85</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -971,6 +1271,31 @@
       <c r="E14">
         <v>234</v>
       </c>
+      <c r="F14">
+        <v>8</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>52.5</v>
+      </c>
+      <c r="I14">
+        <v>37.5</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>89</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -988,6 +1313,31 @@
       <c r="E15">
         <v>251</v>
       </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>45</v>
+      </c>
+      <c r="I15">
+        <v>45</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>75</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1005,8 +1355,33 @@
       <c r="E16">
         <v>159</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>40</v>
+      </c>
+      <c r="I16">
+        <v>32.5</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>72.5</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -1022,8 +1397,33 @@
       <c r="E17">
         <v>246</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>8</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>75</v>
+      </c>
+      <c r="I17">
+        <v>40</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>115</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -1039,8 +1439,33 @@
       <c r="E18">
         <v>268</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>8</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>47.5</v>
+      </c>
+      <c r="I18">
+        <v>55</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>102.5</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -1056,8 +1481,33 @@
       <c r="E19">
         <v>257</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>55</v>
+      </c>
+      <c r="I19">
+        <v>55</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -1073,8 +1523,33 @@
       <c r="E20">
         <v>195</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>55</v>
+      </c>
+      <c r="I20">
+        <v>45</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K20">
+        <v>10</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -1090,8 +1565,33 @@
       <c r="E21">
         <v>219</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>8</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>35</v>
+      </c>
+      <c r="I21">
+        <v>37.5</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>72.5</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -1106,6 +1606,31 @@
       </c>
       <c r="E22">
         <v>168</v>
+      </c>
+      <c r="F22">
+        <v>8</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>45</v>
+      </c>
+      <c r="I22">
+        <v>52.5</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>97.5</v>
+      </c>
+      <c r="K22">
+        <v>10</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1193,6 +1718,31 @@
       <c r="E2">
         <v>161</v>
       </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>70</v>
+      </c>
+      <c r="I2">
+        <v>75</v>
+      </c>
+      <c r="J2">
+        <f>SUM(H2,I2)</f>
+        <v>145</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>93</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1208,7 +1758,32 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>284</v>
+        <v>294</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>110</v>
+      </c>
+      <c r="I3">
+        <v>125</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J19" si="0">SUM(H3,I3)</f>
+        <v>235</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -1227,6 +1802,31 @@
       <c r="E4">
         <v>241</v>
       </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>85</v>
+      </c>
+      <c r="I4">
+        <v>120</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>205</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>134</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1244,6 +1844,31 @@
       <c r="E5">
         <v>184</v>
       </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>65</v>
+      </c>
+      <c r="I5">
+        <v>111</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>176</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>77</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1261,6 +1886,31 @@
       <c r="E6">
         <v>291</v>
       </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>110</v>
+      </c>
+      <c r="I6">
+        <v>130</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>138</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1278,6 +1928,31 @@
       <c r="E7">
         <v>258</v>
       </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>75</v>
+      </c>
+      <c r="I7">
+        <v>75</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>96</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1295,6 +1970,31 @@
       <c r="E8">
         <v>240</v>
       </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>92.5</v>
+      </c>
+      <c r="I8">
+        <v>90</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>182.5</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>131</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1312,6 +2012,31 @@
       <c r="E9">
         <v>195</v>
       </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>87.5</v>
+      </c>
+      <c r="I9">
+        <v>95</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>182.5</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>125</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1329,6 +2054,31 @@
       <c r="E10">
         <v>224</v>
       </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>90</v>
+      </c>
+      <c r="I10">
+        <v>95</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>117</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1346,6 +2096,31 @@
       <c r="E11">
         <v>185</v>
       </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>95</v>
+      </c>
+      <c r="I11">
+        <v>70</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>165</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>138</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1363,6 +2138,31 @@
       <c r="E12">
         <v>230</v>
       </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>115</v>
+      </c>
+      <c r="I12">
+        <v>110</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>225</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>130</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1380,6 +2180,31 @@
       <c r="E13">
         <v>263</v>
       </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>95</v>
+      </c>
+      <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>142</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1397,6 +2222,31 @@
       <c r="E14">
         <v>113</v>
       </c>
+      <c r="F14">
+        <v>8</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1414,6 +2264,31 @@
       <c r="E15">
         <v>265</v>
       </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>97.5</v>
+      </c>
+      <c r="I15">
+        <v>97.5</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>139</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1431,8 +2306,33 @@
       <c r="E16">
         <v>245</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>105</v>
+      </c>
+      <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>205</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>78</v>
       </c>
@@ -1448,8 +2348,33 @@
       <c r="E17">
         <v>206</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>8</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>55</v>
+      </c>
+      <c r="I17">
+        <v>90</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>145</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>79</v>
       </c>
@@ -1465,8 +2390,33 @@
       <c r="E18">
         <v>220</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>8</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>110</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -1481,6 +2431,31 @@
       </c>
       <c r="E19">
         <v>261</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>95</v>
+      </c>
+      <c r="I19">
+        <v>107.5</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>202.5</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\crossfit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540689EB-0AFD-4B62-A03F-00D13729BB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4C14D5-82AF-4E39-8778-F070D3ACB317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
   <sheets>
     <sheet name="ScoreF" sheetId="1" r:id="rId1"/>
@@ -792,6 +792,15 @@
       <c r="M2">
         <v>95</v>
       </c>
+      <c r="N2">
+        <v>10</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1440</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -834,6 +843,15 @@
       <c r="M3">
         <v>154</v>
       </c>
+      <c r="N3">
+        <v>8</v>
+      </c>
+      <c r="O3">
+        <v>6</v>
+      </c>
+      <c r="P3">
+        <v>1580</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -876,6 +894,15 @@
       <c r="M4">
         <v>98</v>
       </c>
+      <c r="N4">
+        <v>9</v>
+      </c>
+      <c r="O4">
+        <v>59</v>
+      </c>
+      <c r="P4">
+        <v>1580</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -918,6 +945,15 @@
       <c r="M5">
         <v>99</v>
       </c>
+      <c r="N5">
+        <v>8</v>
+      </c>
+      <c r="O5">
+        <v>42</v>
+      </c>
+      <c r="P5">
+        <v>1580</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -960,6 +996,15 @@
       <c r="M6">
         <v>138</v>
       </c>
+      <c r="N6">
+        <v>9</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>1580</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1002,6 +1047,15 @@
       <c r="M7">
         <v>90</v>
       </c>
+      <c r="N7">
+        <v>10</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1561</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1044,6 +1098,15 @@
       <c r="M8">
         <v>132</v>
       </c>
+      <c r="N8">
+        <v>8</v>
+      </c>
+      <c r="O8">
+        <v>31</v>
+      </c>
+      <c r="P8">
+        <v>1580</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1086,6 +1149,15 @@
       <c r="M9">
         <v>55</v>
       </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1043</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1128,6 +1200,15 @@
       <c r="M10">
         <v>95</v>
       </c>
+      <c r="N10">
+        <v>10</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1572</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1170,6 +1251,15 @@
       <c r="M11">
         <v>117</v>
       </c>
+      <c r="N11">
+        <v>8</v>
+      </c>
+      <c r="O11">
+        <v>45</v>
+      </c>
+      <c r="P11">
+        <v>1580</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1212,6 +1302,15 @@
       <c r="M12">
         <v>97</v>
       </c>
+      <c r="N12">
+        <v>10</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1560</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1254,6 +1353,15 @@
       <c r="M13">
         <v>85</v>
       </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1170</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1296,6 +1404,15 @@
       <c r="M14">
         <v>89</v>
       </c>
+      <c r="N14">
+        <v>10</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1564</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1338,6 +1455,15 @@
       <c r="M15">
         <v>75</v>
       </c>
+      <c r="N15">
+        <v>10</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1564</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1380,8 +1506,17 @@
       <c r="M16">
         <v>37</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N16">
+        <v>10</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -1422,8 +1557,17 @@
       <c r="M17">
         <v>98</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N17">
+        <v>10</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -1464,8 +1608,17 @@
       <c r="M18">
         <v>103</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N18">
+        <v>9</v>
+      </c>
+      <c r="O18">
+        <v>43</v>
+      </c>
+      <c r="P18">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -1506,8 +1659,17 @@
       <c r="M19">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N19">
+        <v>10</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -1548,8 +1710,17 @@
       <c r="M20">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N20">
+        <v>10</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -1590,8 +1761,17 @@
       <c r="M21">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N21">
+        <v>10</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -1631,6 +1811,15 @@
       </c>
       <c r="M22">
         <v>95</v>
+      </c>
+      <c r="N22">
+        <v>10</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1569</v>
       </c>
     </row>
   </sheetData>
@@ -1743,6 +1932,15 @@
       <c r="M2">
         <v>93</v>
       </c>
+      <c r="N2">
+        <v>10</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1240</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1785,6 +1983,15 @@
       <c r="M3">
         <v>161</v>
       </c>
+      <c r="N3">
+        <v>7</v>
+      </c>
+      <c r="O3">
+        <v>31</v>
+      </c>
+      <c r="P3">
+        <v>1880</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1827,6 +2034,15 @@
       <c r="M4">
         <v>134</v>
       </c>
+      <c r="N4">
+        <v>9</v>
+      </c>
+      <c r="O4">
+        <v>8</v>
+      </c>
+      <c r="P4">
+        <v>1880</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1911,6 +2127,15 @@
       <c r="M6">
         <v>138</v>
       </c>
+      <c r="N6">
+        <v>7</v>
+      </c>
+      <c r="O6">
+        <v>42</v>
+      </c>
+      <c r="P6">
+        <v>1880</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1953,6 +2178,15 @@
       <c r="M7">
         <v>96</v>
       </c>
+      <c r="N7">
+        <v>10</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1865</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1995,6 +2229,15 @@
       <c r="M8">
         <v>131</v>
       </c>
+      <c r="N8">
+        <v>8</v>
+      </c>
+      <c r="O8">
+        <v>51</v>
+      </c>
+      <c r="P8">
+        <v>1880</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -2079,6 +2322,15 @@
       <c r="M10">
         <v>117</v>
       </c>
+      <c r="N10">
+        <v>9</v>
+      </c>
+      <c r="O10">
+        <v>36</v>
+      </c>
+      <c r="P10">
+        <v>1880</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -2121,6 +2373,15 @@
       <c r="M11">
         <v>138</v>
       </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1874</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -2163,6 +2424,15 @@
       <c r="M12">
         <v>130</v>
       </c>
+      <c r="N12">
+        <v>9</v>
+      </c>
+      <c r="O12">
+        <v>8</v>
+      </c>
+      <c r="P12">
+        <v>1880</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -2205,6 +2475,15 @@
       <c r="M13">
         <v>142</v>
       </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1880</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -2247,6 +2526,15 @@
       <c r="M14">
         <v>0</v>
       </c>
+      <c r="N14">
+        <v>10</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -2289,6 +2577,15 @@
       <c r="M15">
         <v>139</v>
       </c>
+      <c r="N15">
+        <v>7</v>
+      </c>
+      <c r="O15">
+        <v>56</v>
+      </c>
+      <c r="P15">
+        <v>1880</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -2331,8 +2628,17 @@
       <c r="M16">
         <v>122</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N16">
+        <v>10</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>78</v>
       </c>
@@ -2374,7 +2680,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>79</v>
       </c>
@@ -2415,8 +2721,17 @@
       <c r="M18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N18">
+        <v>8</v>
+      </c>
+      <c r="O18">
+        <v>57</v>
+      </c>
+      <c r="P18">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>96</v>
       </c>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\crossfit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4C14D5-82AF-4E39-8778-F070D3ACB317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C4D4C4-C0DD-4817-9DC4-E990B8419E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
   <sheets>
     <sheet name="ScoreF" sheetId="1" r:id="rId1"/>
@@ -2085,6 +2085,15 @@
       <c r="M5">
         <v>77</v>
       </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1869</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -2280,6 +2289,15 @@
       <c r="M9">
         <v>125</v>
       </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1870</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -2679,6 +2697,15 @@
       <c r="M17">
         <v>77</v>
       </c>
+      <c r="N17">
+        <v>10</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1636</v>
+      </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -2771,6 +2798,15 @@
       </c>
       <c r="M19">
         <v>133</v>
+      </c>
+      <c r="N19">
+        <v>8</v>
+      </c>
+      <c r="O19">
+        <v>4</v>
+      </c>
+      <c r="P19">
+        <v>1880</v>
       </c>
     </row>
   </sheetData>
